--- a/vulnerability_test/vulnerability_test_report.xlsx
+++ b/vulnerability_test/vulnerability_test_report.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Cookie Security</t>
+          <t>Cookie Security - Transport</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify expired sessions are systematically removed from persistent datastore.</t>
+          <t>Verify expired sessions are systematically removed from database.</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -1179,17 +1179,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 21</t>
+          <t>Authentication check on WebSocket connection handshakes</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>WebSocket Security</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 21 when utilizing invalid state formats.</t>
+          <t>Verify WebSocket connections reject connections without valid auth token parameters.</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 22</t>
+          <t>Remember Me token encryption and hash storage check</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Remember Me Token Protection</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 22 when utilizing invalid state formats.</t>
+          <t>Verify remember-me tokens are hashed in database before validation lookup.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 23</t>
+          <t>Automatic session lock after 15 minutes of idle state</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Inactivity Timeout</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 23 when utilizing invalid state formats.</t>
+          <t>Verify system logs out users who perform no actions for 15 minutes.</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 24</t>
+          <t>Supabase session persistence decryption check on reload</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Session Decryption</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 24 when utilizing invalid state formats.</t>
+          <t>Verify stored sessions are authenticated and decoded on fresh reload.</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 25</t>
+          <t>Validation of password reset link signature parameter</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Token Integrity</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 25 when utilizing invalid state formats.</t>
+          <t>Verify modifying reset link signature parameter renders token invalid.</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 26</t>
+          <t>Password recovery input email domain whitelist enforcement</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Auth Domain Check</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 26 when utilizing invalid state formats.</t>
+          <t>Verify recovery requests only accept valid email domain strings.</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 27</t>
+          <t>Multi-tab browser sync for active auth token state changes</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Session Sync</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 27 when utilizing invalid state formats.</t>
+          <t>Verify standard tabs share live session states to block zombie requests.</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 28</t>
+          <t>Single sign-out logic verification across active clients</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Auth Sync Invalidation</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 28 when utilizing invalid state formats.</t>
+          <t>Verify logging out on mobile clears active sessions on other platforms.</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 29</t>
+          <t>Verification of OTP verification code format limits</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Input Validation Rules</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 29 when utilizing invalid state formats.</t>
+          <t>Verify OTP codes reject non-numeric digits or characters on input.</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1467,17 +1467,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 30</t>
+          <t>Enforcement of minimum signup field requirements verification</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Input Presence Validation</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 30 when utilizing invalid state formats.</t>
+          <t>Verify registration form blocks missing email/password field entries.</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 31</t>
+          <t>Validation of custom auth headers in private server routes</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Headers Verification</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 31 when utilizing invalid state formats.</t>
+          <t>Verify client credentials in custom auth headers match secure server config.</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 32</t>
+          <t>Password complexity check rejecting repeated character patterns</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Entropy Enforcement</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 32 when utilizing invalid state formats.</t>
+          <t>Verify passwords containing sequential strings (e.g. 12345) are rejected.</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -1563,17 +1563,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 33</t>
+          <t>Validation of reset password flow password match criteria</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Match Validation</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 33 when utilizing invalid state formats.</t>
+          <t>Verify confirmation password field must match new password field inputs.</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 34</t>
+          <t>Checking account lookup responses for Timing Attack leaks</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Timing Attack Defense</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 34 when utilizing invalid state formats.</t>
+          <t>Verify database response delays are identical for existing and non-existing email queries.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 35</t>
+          <t>Verification of user password change re-authentication rules</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Privileged Re-Auth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 35 when utilizing invalid state formats.</t>
+          <t>Verify changing password requires current password verification first.</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1659,17 +1659,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 36</t>
+          <t>Validation of session cache cleanup on page unmount event</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Cache Protection</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 36 when utilizing invalid state formats.</t>
+          <t>Verify state storage variables are wiped from memory on tab close.</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 37</t>
+          <t>Verification of token storage limits in LocalStorage limits</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Quota Security</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 37 when utilizing invalid state formats.</t>
+          <t>Verify auth client restricts payload storage sizes to prevent browser crash.</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -1723,17 +1723,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 38</t>
+          <t>Checking refresh token single-use rotation execution policy</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Refresh Token Rotation</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 38 when utilizing invalid state formats.</t>
+          <t>Verify requesting new access token consumes and invalidates old refresh token.</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 39</t>
+          <t>Checking brute force delay duration increase logic verify</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Login Backoff Lockout</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 39 when utilizing invalid state formats.</t>
+          <t>Verify successive failed logins double backoff delays automatically.</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -1787,17 +1787,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Session control verify for endpoint context type 40</t>
+          <t>Verification of captcha challenge trigger on failed logins</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Session Validation</t>
+          <t>Automated Sign-in Block</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Verify that session validation routines reject requests for scenario template configuration 40 when utilizing invalid state formats.</t>
+          <t>Verify captcha prompt fires after 3 consecutive failed login queries.</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>BOLA validation on case update/edit status API requests</t>
+          <t>BOLA validation on lab attachment delete endpoint calls</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify modifying patient details requires original creator permission.</t>
+          <t>Verify delete attachment calls reject requests from outside the linked lab.</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>BOLA validation on lab attachment delete endpoint calls</t>
+          <t>BOLA validation on procedures configuration updates</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify delete attachment calls reject requests from outside the linked lab.</t>
+          <t>Verify standard users cannot write/update general procedure reference lists.</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>BOLA validation on procedures configuration updates</t>
+          <t>BFLA restriction on doctor registration approval API calls</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>IDOR Prevention</t>
+          <t>Privilege Escalation Defense</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify standard users cannot write/update general procedure reference lists.</t>
+          <t>Verify standard doctors/labs cannot post approval triggers to the org endpoint.</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>BFLA restriction on doctor registration approval API calls</t>
+          <t>BFLA restriction on organization dashboard config edits</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Verify standard doctors/labs cannot post approval triggers to the org endpoint.</t>
+          <t>Verify doctor accounts are blocked from accessing organization dashboard API configurations.</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>BFLA restriction on organization dashboard config edits</t>
+          <t>BFLA restriction on database migration execute actions</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Privilege Escalation Defense</t>
+          <t>Administrative Lockout</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Verify doctor accounts are blocked from accessing organization dashboard API configurations.</t>
+          <t>Verify only superusers can invoke schema updates on backend database systems.</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>BFLA restriction on database migration execute actions</t>
+          <t>BFLA restriction on user blocking/unblocking actions</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Administrative Lockout</t>
+          <t>Privilege Escalation Defense</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Verify only superusers can invoke schema updates on backend database systems.</t>
+          <t>Verify lab technicians cannot block/unblock other users in the org.</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>BFLA restriction on user blocking/unblocking actions</t>
+          <t>BFLA restriction on clinical staff list updates</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verify lab technicians cannot block/unblock other users in the org.</t>
+          <t>Verify organization workspace endpoints require Clinic Org admin privileges.</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>BFLA restriction on clinical staff list updates</t>
+          <t>Horizontal privilege check on clinical cases list filter queries</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Privilege Escalation Defense</t>
+          <t>Horizontal Separation</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify organization workspace endpoints require Clinic Org admin privileges.</t>
+          <t>Verify filtering cases returns only records within user's organization boundary.</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -2139,17 +2139,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Horizontal privilege check on clinical cases list filter queries</t>
+          <t>Vertical privilege check on user role modification requests</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Horizontal Separation</t>
+          <t>Vertical Separation</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify filtering cases returns only records within user's organization boundary.</t>
+          <t>Verify submitting role modification payload (e.g. changing role to admin) fails.</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Vertical privilege check on user role modification requests</t>
+          <t>Tenant isolation validation on Supabase Row Level Security (RLS)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Vertical Separation</t>
+          <t>Row Level Security</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Verify submitting role modification payload (e.g. changing role to admin) fails.</t>
+          <t>Verify Supabase policies restrict read/write of tables matching tenant ID.</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -2203,17 +2203,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Tenant isolation validation on Supabase Row Level Security (RLS)</t>
+          <t>Static code path bypass validation on private routing middleware</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Row Level Security</t>
+          <t>Navigation Guard</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Verify Supabase policies restrict read/write of tables matching tenant ID.</t>
+          <t>Verify direct URL access of dashboard layouts checks role before render.</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
@@ -2235,17 +2235,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Static code path bypass validation on private routing middleware</t>
+          <t>Token scope verification on custom API handlers</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Navigation Guard</t>
+          <t>Scope Validation</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verify direct URL access of dashboard layouts checks role before render.</t>
+          <t>Verify authorization claims contain appropriate scopes before returning payloads.</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Token scope verification on custom API handlers</t>
+          <t>Broken Object level checks on doctor directory file exports</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Scope Validation</t>
+          <t>BOLA Prevention</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Verify authorization claims contain appropriate scopes before returning payloads.</t>
+          <t>Verify exporting doctors database requires master admin authority levels.</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
@@ -2299,17 +2299,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 56</t>
+          <t>Tenant isolation checks on global analytics dashboard feeds</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Multi-tenant Isolation</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 56.</t>
+          <t>Verify organization analytics graphs hide other tenant company statistics.</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -2331,17 +2331,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 57</t>
+          <t>Access control validation on API swagger metadata documentation</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Information Leakage Guard</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 57.</t>
+          <t>Verify documentation paths are blocked on production servers for standard profiles.</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 58</t>
+          <t>Check path parameter privilege escalation on details page</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>URL Parameter Guard</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 58.</t>
+          <t>Verify editing URL parameters (e.g. id=999) does not bypass role blocks.</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 59</t>
+          <t>Broken access control verify on user profile avatar save</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Resource Authorization</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 59.</t>
+          <t>Verify updating profile images requires matching auth user ID ownership.</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 60</t>
+          <t>Broken access control validation on clinic configuration values</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>BFLA Prevention</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 60.</t>
+          <t>Verify regular doctor accounts cannot modify corporate metadata settings.</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 61</t>
+          <t>Security control check on case delegation action permissions</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Role Constraints</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 61.</t>
+          <t>Verify only clinic owners can delegate cases to external lab teams.</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 62</t>
+          <t>Authorization check on notification trigger system endpoints</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Access Controls</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 62.</t>
+          <t>Verify notification send triggers cannot be fired by guest user calls.</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -2523,17 +2523,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 63</t>
+          <t>BOLA validation on doctor schedules list query settings</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>IDOR Prevention</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 63.</t>
+          <t>Verify querying doctor calendar schedules blocks access to other doctors' times.</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 64</t>
+          <t>BOLA validation on patient clinical history timelines view</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>IDOR Prevention</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 64.</t>
+          <t>Verify patient history requests validate active doctor link constraints.</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -2587,17 +2587,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 65</t>
+          <t>BOLA validation on document attachments fetch API routes</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>IDOR Prevention</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 65.</t>
+          <t>Verify fetching diagnostic file attachments checks ownership access lists.</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -2619,17 +2619,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 66</t>
+          <t>BFLA check on user invitation token generation requests</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Privilege Escalation Defense</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 66.</t>
+          <t>Verify standard accounts cannot create invitation tokens for new admins.</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 67</t>
+          <t>BFLA check on database config settings update endpoint</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Administrative Access Guard</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 67.</t>
+          <t>Verify REST configurations reject update payloads from regular profiles.</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -2683,17 +2683,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 68</t>
+          <t>Horizontal validation check on patient archive pagination search</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Tenant Separation</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 68.</t>
+          <t>Verify paging patient lists returns only records in active clinic partition.</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -2715,17 +2715,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 69</t>
+          <t>Vertical validation check on system maintenance tools trigger</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Role Separation</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 69.</t>
+          <t>Verify system maintenance API paths block access to all standard users.</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 70</t>
+          <t>Broken Object level check on patient treatment notes update</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>IDOR Protection</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 70.</t>
+          <t>Verify updating treatment notes validates current clinician ownership fields.</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 71</t>
+          <t>Broken Function level check on system backup triggers API</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Administrative Guardout</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 71.</t>
+          <t>Verify system backup endpoints reject non-admin API tokens.</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -2811,17 +2811,17 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 72</t>
+          <t>Horizontal check on dashboard active counts widget queries</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Tenant Partition Check</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 72.</t>
+          <t>Verify count summary queries only target current organization database partition.</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 73</t>
+          <t>Vertical check on password override administrative endpoint</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Role Partition Check</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 73.</t>
+          <t>Verify admin password override endpoints block non-superadmin credentials.</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 74</t>
+          <t>Validation of session validation guards in routing modules</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Router Guard Verification</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 74.</t>
+          <t>Verify routing middleware blocks view renders before token verify checks.</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -2907,17 +2907,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 75</t>
+          <t>Validation of RLS policies on Supabase auth profiles metadata</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>Row Level Security</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 75.</t>
+          <t>Verify user profile rows can only be updated by the corresponding auth owner.</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -2934,22 +2934,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Access Control (Authorization)</t>
+          <t>Injection Vulnerabilities</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 76</t>
+          <t>SQL Injection check on login authentication fields</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>SQLi Prevention</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 76.</t>
+          <t>Verify input sanitization on email/password fields blocks SQL meta-characters.</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -2966,22 +2966,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Access Control (Authorization)</t>
+          <t>Injection Vulnerabilities</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 77</t>
+          <t>SQL Injection check on patient search query inputs</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>SQLi Prevention</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 77.</t>
+          <t>Verify parameterized queries are utilized in search database execution path.</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
@@ -2998,22 +2998,22 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Access Control (Authorization)</t>
+          <t>Injection Vulnerabilities</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 78</t>
+          <t>Stored XSS check on patient name input form inputs</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>XSS Prevention</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 78.</t>
+          <t>Verify html entity encoding on patient name prevents stored script execution.</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Access Control (Authorization)</t>
+          <t>Injection Vulnerabilities</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 79</t>
+          <t>Stored XSS check on diagnosis comments textareas</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>XSS Prevention</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 79.</t>
+          <t>Verify diagnostic descriptions parse script tags as strings, avoiding DOM triggers.</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
@@ -3062,22 +3062,22 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Access Control (Authorization)</t>
+          <t>Injection Vulnerabilities</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Privilege separation logic query for context model 80</t>
+          <t>Reflected XSS check on dashboard search parameters in URLs</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Authorization Lockout</t>
+          <t>XSS Prevention</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Verify that authorization logic denies unauthorized role access to service endpoint component configuration 80.</t>
+          <t>Verify query parameters printed in page layout are escaped to block execution.</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -3099,17 +3099,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>SQL Injection check on login authentication fields</t>
+          <t>DOM-based XSS check on custom markdown rendering logic</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>SQLi Prevention</t>
+          <t>XSS Prevention</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Verify input sanitization on email/password fields blocks SQL meta-characters.</t>
+          <t>Verify markdown rendering engines sanitize HTML output to prevent link injection XSS.</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
@@ -3131,17 +3131,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>SQL Injection check on patient search query inputs</t>
+          <t>OS Command Injection check on attachment PDF name processors</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>SQLi Prevention</t>
+          <t>Command Injection Block</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Verify parameterized queries are utilized in search database execution path.</t>
+          <t>Verify file process commands do not execute arbitrary shell strings.</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -3163,17 +3163,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>SQL Injection check on reports filter dates input fields</t>
+          <t>NoSQL Injection check on database analytics query inputs</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>SQLi Prevention</t>
+          <t>NoSQL Injection Block</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Verify custom date filters sanitize string inputs before SQL compilation.</t>
+          <t>Verify JSON queries validate key structures to block NoSQL logic injection.</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>SQL Injection check on organization registration fields</t>
+          <t>HTML Injection check on custom PDF report builders</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>SQLi Prevention</t>
+          <t>HTML Injection Block</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Verify organization lookup fields escape quotes to prevent database corruption.</t>
+          <t>Verify PDF generators sanitize HTML inputs to prevent arbitrary layout modification.</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -3227,17 +3227,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Stored XSS check on patient name input form inputs</t>
+          <t>Log Injection check on warning logging message paths</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>XSS Prevention</t>
+          <t>Log Sanitization</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Verify html entity encoding on patient name prevents stored script execution.</t>
+          <t>Verify newline characters are stripped from user logs to prevent log spoofing.</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Stored XSS check on diagnosis comments textareas</t>
+          <t>LDAP Injection check on organization address lookup services</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>XSS Prevention</t>
+          <t>LDAP Injection Block</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Verify diagnostic descriptions parse script tags as strings, avoiding DOM triggers.</t>
+          <t>Verify address query arguments parse criteria strictly without LDAP triggers.</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -3291,17 +3291,17 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Stored XSS check on lab results comments textareas</t>
+          <t>XPath Injection check on configuration XML parser modules</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>XSS Prevention</t>
+          <t>XPath Injection Block</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Verify laboratory comments do not execute script inputs when viewed by doctors.</t>
+          <t>Verify XML configurations reject query manipulations and nested commands.</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
@@ -3323,17 +3323,17 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Reflected XSS check on dashboard search parameters in URLs</t>
+          <t>SQL Injection check on doctor registration registration form</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>XSS Prevention</t>
+          <t>SQLi Prevention</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Verify query parameters printed in page layout are escaped to block execution.</t>
+          <t>Verify license registration input parameters escape single quote characters.</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -3355,17 +3355,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>DOM-based XSS check on custom markdown rendering logic</t>
+          <t>SQL Injection check on clinical procedure deletion queries</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>XSS Prevention</t>
+          <t>SQLi Prevention</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Verify markdown rendering engines sanitize HTML output to prevent link injection XSS.</t>
+          <t>Verify procedure code inputs are type-cast to integers to block injection.</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>OS Command Injection check on attachment PDF name processors</t>
+          <t>Stored XSS check on doctor profile credentials text field</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Command Injection Block</t>
+          <t>XSS Prevention</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Verify file process commands do not execute arbitrary shell strings.</t>
+          <t>Verify qualifications field text blocks and strips nested iframe components.</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -3419,17 +3419,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>NoSQL Injection check on database analytics query inputs</t>
+          <t>HTML Injection check on notification email dispatch templates</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>NoSQL Injection Block</t>
+          <t>HTML Injection Block</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Verify JSON queries validate key structures to block NoSQL logic injection.</t>
+          <t>Verify email bodies escape username variables to block layout injection.</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -3451,17 +3451,17 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>HTML Injection check on custom PDF report builders</t>
+          <t>Log Injection check on access error reporting modules</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>HTML Injection Block</t>
+          <t>Log Sanitization</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Verify PDF generators sanitize HTML inputs to prevent arbitrary layout modification.</t>
+          <t>Verify login attempt usernames are formatted to remove return characters.</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -3483,17 +3483,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Log Injection check on warning logging message paths</t>
+          <t>XML Entity Injection check on incoming XML metadata files</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Log Sanitization</t>
+          <t>XXE Prevention</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Verify newline characters are stripped from user logs to prevent log spoofing.</t>
+          <t>Verify XML parser limits nested element processing to disable DTD parses.</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -3515,17 +3515,17 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>LDAP Injection check on organization address lookup services</t>
+          <t>XPath Injection check on permissions lookup service files</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>LDAP Injection Block</t>
+          <t>XPath Injection Block</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verify address query arguments parse criteria strictly without LDAP triggers.</t>
+          <t>Verify system directory searches filter wildcard symbols from lookup inputs.</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>XPath Injection check on configuration XML parser modules</t>
+          <t>Header Injection check on API redirect routing components</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>XPath Injection Block</t>
+          <t>HTTP Response Splitting</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Verify XML configurations reject query manipulations and nested commands.</t>
+          <t>Verify newline characters are removed from location redirect inputs.</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 96</t>
+          <t>SSRF validation check on organization logo URL inputs</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>SSRF Protection</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 96 to prevent query manipulation.</t>
+          <t>Verify logo URL targets resolve to public addresses, blocking local network IPs.</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 97</t>
+          <t>Template Injection check on patient intake form formats</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>SSTI Prevention</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 97 to prevent query manipulation.</t>
+          <t>Verify templating engines process form names without template tag evaluations.</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
@@ -3643,17 +3643,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 98</t>
+          <t>OS Command check on diagnostic scan upload zip extracts</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Command Injection Block</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 98 to prevent query manipulation.</t>
+          <t>Verify file names in extracted archives avoid executing system path updates.</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -3675,17 +3675,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 99</t>
+          <t>NoSQL check on authentication profile document query</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>NoSQL Injection Block</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 99 to prevent query manipulation.</t>
+          <t>Verify key matching routines check document types to block wildcard queries.</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -3707,17 +3707,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 100</t>
+          <t>HTML check on invoice print template styling parameters</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>HTML Injection Block</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 100 to prevent query manipulation.</t>
+          <t>Verify stylesheet imports filter script links before PDF rendering.</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 101</t>
+          <t>Log check on Supabase connection handshake warning reports</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Log Sanitization</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 101 to prevent query manipulation.</t>
+          <t>Verify connection URL strings strip credentials before storage logging.</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 102</t>
+          <t>XML External Entity check on clinical guide layout uploads</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>XXE Protection</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 102 to prevent query manipulation.</t>
+          <t>Verify parsing schema files disables entity resolution parameters.</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 103</t>
+          <t>SSRF check on web webhook registration callback URLs</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>SSRF Protection</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 103 to prevent query manipulation.</t>
+          <t>Verify webhook targets reject loopback addresses (127.0.0.1) and private subnets.</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
@@ -3830,22 +3830,22 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 104</t>
+          <t>Unrestricted file upload validation for script formats (PHP, JS)</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>File Type Verification</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 104 to prevent query manipulation.</t>
+          <t>Verify uploads block files ending in script extensions (e.g. .php, .js).</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -3862,22 +3862,22 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 105</t>
+          <t>Executable file upload check for system binary formats (EXE, ELF)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>File Type Verification</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 105 to prevent query manipulation.</t>
+          <t>Verify uploads block executables to prevent remote execution on storage.</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -3894,22 +3894,22 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 106</t>
+          <t>MIME-type validation checks on diagnostic images uploaded</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>MIME Validation</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 106 to prevent query manipulation.</t>
+          <t>Verify file parser checks file signature header, not just file extensions.</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -3926,22 +3926,22 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 107</t>
+          <t>SVG file uploads XML External Entity (XXE) injection checks</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>XXE Prevention</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 107 to prevent query manipulation.</t>
+          <t>Verify SVG image parser disables external entities to prevent server file read.</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -3958,22 +3958,22 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 108</t>
+          <t>File size limits verification on attachment upload paths</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>File Size Restriction</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 108 to prevent query manipulation.</t>
+          <t>Verify uploading large diagnostic scans exceeding 50MB is rejected.</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -3990,22 +3990,22 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 109</t>
+          <t>Path Traversal check on filename parameter in download requests</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Path Traversal Block</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 109 to prevent query manipulation.</t>
+          <t>Verify directory traversal tags (../) are stripped from filename parameter.</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 110</t>
+          <t>Path Traversal check on report output directory path configurations</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Path Traversal Block</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 110 to prevent query manipulation.</t>
+          <t>Verify output paths remain locked within designated target folders.</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -4054,22 +4054,22 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 111</t>
+          <t>Absolute path parameter injection validation on storage downloads</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Path Traversal Block</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 111 to prevent query manipulation.</t>
+          <t>Verify path inputs do not resolve to system files (e.g. /etc/passwd).</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -4086,22 +4086,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 112</t>
+          <t>Metadata sanitization verification on uploaded diagnostic images</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Metadata Stripping</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 112 to prevent query manipulation.</t>
+          <t>Verify EXIF GPS location tags are stripped from patient images to protect PII.</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -4118,22 +4118,22 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 113</t>
+          <t>File upload name normalization checks on backend file storage</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Filename Sanitization</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 113 to prevent query manipulation.</t>
+          <t>Verify uploaded names are rewritten to UUIDs to prevent file overwrites.</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
@@ -4150,22 +4150,22 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 114</t>
+          <t>HTML type file upload cross-site script validation</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>File Validation</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 114 to prevent query manipulation.</t>
+          <t>Verify files with HTML extension are rejected in diagnostic uploads.</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -4182,22 +4182,22 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 115</t>
+          <t>Zip bomb decompression denial of service checks</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Decompression Defense</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 115 to prevent query manipulation.</t>
+          <t>Verify zip extraction libraries limit extracted payload size to prevent DoS.</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 116</t>
+          <t>Null byte injection checks on upload target filename parameters</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Null Byte Prevention</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 116 to prevent query manipulation.</t>
+          <t>Verify null bytes (.php%00.jpg) do not bypass extension checks.</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -4246,22 +4246,22 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 117</t>
+          <t>Symbolic link upload file traversal vulnerability checks</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Symlink Prevention</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 117 to prevent query manipulation.</t>
+          <t>Verify archive extraction ignores symlinks to prevent server reads.</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 118</t>
+          <t>Double extension file upload check on diagnostic scan uploads</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Double Extension Check</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 118 to prevent query manipulation.</t>
+          <t>Verify files with multiple extensions (e.g. doc.png.php) are rejected.</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 119</t>
+          <t>Malicious file signature scanning check on uploads stream</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Virus Scanner Integration</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 119 to prevent query manipulation.</t>
+          <t>Verify file stream is scanned via antivirus before storage save.</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Injection Vulnerabilities</t>
+          <t>File Upload &amp; Path Traversal</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Input injection sanitize logic verify on interface parameter 120</t>
+          <t>Checking directory traversal validation on path configs</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Input Sanitization</t>
+          <t>Path Traversal Prevention</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Verify that input fields sanitize payload values for configuration interface template 120 to prevent query manipulation.</t>
+          <t>Verify configuration paths reject backslash characters to block directory escapes.</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -4379,17 +4379,17 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Unrestricted file upload validation for script formats (PHP, JS)</t>
+          <t>Check filename truncation issues during attachment extraction</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>File Type Verification</t>
+          <t>Filename Sanitization Rules</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Verify uploads block files ending in script extensions (e.g. .php, .js).</t>
+          <t>Verify name parsing limits length to prevent buffer overruns.</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -4411,17 +4411,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Executable file upload check for system binary formats (EXE, ELF)</t>
+          <t>Validation of file access logs for private diagnostic files</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>File Type Verification</t>
+          <t>Access Logs Verification</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Verify uploads block executables to prevent remote execution on storage.</t>
+          <t>Verify system records filename and requester details on downloads.</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -4443,17 +4443,17 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>MIME-type validation checks on diagnostic images uploaded</t>
+          <t>Validation of uploads storage partitions isolation settings</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>MIME Validation</t>
+          <t>Storage Partition Isolation</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Verify file parser checks file signature header, not just file extensions.</t>
+          <t>Verify tenant uploads are saved in isolated subdirectory buckets.</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -4475,17 +4475,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>SVG file uploads XML External Entity (XXE) injection checks</t>
+          <t>Verification of directory creation permission on upload endpoints</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>XXE Prevention</t>
+          <t>Storage Access Restrictions</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Verify SVG image parser disables external entities to prevent server file read.</t>
+          <t>Verify upload APIs cannot create folders outside defined directories.</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -4507,17 +4507,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>File size limits verification on attachment upload paths</t>
+          <t>Verification of download bandwidth quota enforcement checks</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>File Size Restriction</t>
+          <t>Download Quota Enforcement</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Verify uploading large diagnostic scans exceeding 50MB is rejected.</t>
+          <t>Verify download rates are restricted per profile to prevent DoS.</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Path Traversal check on filename parameter in download requests</t>
+          <t>Path Traversal check on diagnostic scan retrieval routes</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Verify directory traversal tags (../) are stripped from filename parameter.</t>
+          <t>Verify file path identifiers are matched against database files exclusively.</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Path Traversal check on report output directory path configurations</t>
+          <t>Absolute path query block on PDF output file creators</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Verify output paths remain locked within designated target folders.</t>
+          <t>Verify output generator only writes files inside system temp directories.</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
@@ -4603,17 +4603,17 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Absolute path parameter injection validation on storage downloads</t>
+          <t>Double extension check on laboratory report zip packages</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Path Traversal Block</t>
+          <t>Double Extension Check</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Verify path inputs do not resolve to system files (e.g. /etc/passwd).</t>
+          <t>Verify archive extraction rejects packages containing double-extension files.</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -4635,17 +4635,17 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Metadata sanitization verification on uploaded diagnostic images</t>
+          <t>MIME type verification check on clinic logo asset uploads</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Metadata Stripping</t>
+          <t>MIME Verification</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Verify EXIF GPS location tags are stripped from patient images to protect PII.</t>
+          <t>Verify logo image uploads check file magic bytes for valid PNG/JPG formats.</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -4667,17 +4667,17 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>File upload name normalization checks on backend file storage</t>
+          <t>MIME type verification check on patient reports attachments</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Filename Sanitization</t>
+          <t>MIME Verification</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Verify uploaded names are rewritten to UUIDs to prevent file overwrites.</t>
+          <t>Verify report uploads validate document formats match PDF structures.</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -4699,17 +4699,17 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>HTML type file upload cross-site script validation</t>
+          <t>Verification of file system execution block on storage directory</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>File Validation</t>
+          <t>No-Execute Configuration</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Verify files with HTML extension are rejected in diagnostic uploads.</t>
+          <t>Verify storage subdirectory configuration blocks script executions.</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Zip bomb decompression denial of service checks</t>
+          <t>Verification of file overwrite blocks on diagnostic uploads</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Decompression Defense</t>
+          <t>Storage Isolation Checks</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Verify zip extraction libraries limit extracted payload size to prevent DoS.</t>
+          <t>Verify saving files with identical names creates unique filenames.</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -4763,17 +4763,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Null byte injection checks on upload target filename parameters</t>
+          <t>Checking filename special characters filter logic verify</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Null Byte Prevention</t>
+          <t>Filename Sanitization</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Verify null bytes (.php%00.jpg) do not bypass extension checks.</t>
+          <t>Verify system strips control characters and space symbols from filenames.</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -4795,17 +4795,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Empty file size upload rejection validation on media API</t>
+          <t>Checking null byte filter implementation on file path queries</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>File Size Restriction</t>
+          <t>Null Byte Prevention</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Verify zero-byte files are rejected to prevent file system noise.</t>
+          <t>Verify file system query strings reject null character sequences.</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -4827,17 +4827,17 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Symbolic link upload file traversal vulnerability checks</t>
+          <t>Validation of temp file cleaning routines in storage controllers</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Symlink Prevention</t>
+          <t>Temp File Cleanup</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Verify archive extraction ignores symlinks to prevent server reads.</t>
+          <t>Verify temporary files are purged automatically after api response.</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -4859,17 +4859,17 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 136</t>
+          <t>Validation of upload rates constraint check on storage routes</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Rate Limiting Checks</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 136.</t>
+          <t>Verify system restricts upload frequency to block storage space exhaustion.</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -4891,17 +4891,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 137</t>
+          <t>Symlink extraction block on bulk case file download imports</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Symlink Prevention</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 137.</t>
+          <t>Verify import extraction tools ignore symlink nodes in tar packages.</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -4923,17 +4923,17 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 138</t>
+          <t>Checking file type validation overrides check on image api</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Override Prevention</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 138.</t>
+          <t>Verify system rejects files if content-type header differs from signature.</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -4950,22 +4950,22 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 139</t>
+          <t>Parameter tampering checks on patient age input constraints</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Business Rule Check</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 139.</t>
+          <t>Verify backend validates and rejects negative ages or values &gt; 120.</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -4982,22 +4982,22 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 140</t>
+          <t>Parameter tampering checks on clinical procedure price inputs</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Transaction Validation</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 140.</t>
+          <t>Verify modifying procedure values in request does not update price.</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -5014,22 +5014,22 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 141</t>
+          <t>Bypassing patient approval logic sequence checkpoints</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Workflows Verification</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 141.</t>
+          <t>Verify case reports cannot generate before approval status is confirmed.</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
@@ -5046,22 +5046,22 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 142</t>
+          <t>Modifying completed cases status fields after completion date</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Data Integrity Guard</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 142.</t>
+          <t>Verify completed cases block further updates to clinical notes.</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -5078,22 +5078,22 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 143</t>
+          <t>Deleting case records historical records audit validation</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Audit Validation</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 143.</t>
+          <t>Verify case deletion requires supervisor password validation step.</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
@@ -5110,22 +5110,22 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 144</t>
+          <t>State machine transition checks on lab requisition workflows</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>State Machine Check</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 144.</t>
+          <t>Verify in-progress lab cases cannot transition back to pending status.</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -5142,22 +5142,22 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 145</t>
+          <t>Concurrent submission race conditions check on doctor case creation</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Race Condition Check</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 145.</t>
+          <t>Verify rapid concurrent double-clicks do not create duplicate database rows.</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
@@ -5174,22 +5174,22 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 146</t>
+          <t>Requisition ticket count overflow validation checks</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Numeric Overflow Check</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 146.</t>
+          <t>Verify inputs handle numeric overflow without database type errors.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 147</t>
+          <t>Bypassing organization sign-up confirmation step checkpoints</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Workflow Verification</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 147.</t>
+          <t>Verify account activation requires valid email OTP confirmation.</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
@@ -5238,22 +5238,22 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 148</t>
+          <t>Bypassing patient registration check on new case requisitions</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Constraint Verification</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 148.</t>
+          <t>Verify case creation checks if patient ID exists in records table.</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -5270,22 +5270,22 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 149</t>
+          <t>Schema structure validation verification on custom JSON endpoints</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>JSON Schema Validation</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 149.</t>
+          <t>Verify API blocks payloads with unexpected or extra JSON properties.</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
@@ -5302,22 +5302,22 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 150</t>
+          <t>HTTP verb tunneling prevention validation on REST API routes</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Verb Invalidation Check</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 150.</t>
+          <t>Verify POST requests spoofing GET/DELETE headers fail.</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -5334,22 +5334,22 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 151</t>
+          <t>Empty query parameter bounds validation on bulk query API</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Pagination Boundary Check</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 151.</t>
+          <t>Verify querying without limits sets defaults to prevent memory overload.</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -5366,22 +5366,22 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 152</t>
+          <t>Bypassing email validation constraints during user profile update</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Email Constraint Validation</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 152.</t>
+          <t>Verify email changes trigger re-verification code sequence.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -5398,22 +5398,22 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 153</t>
+          <t>Duplicate registration validation on active email profiles</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Constraint Verification</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 153.</t>
+          <t>Verify registering with an existing email rejects request cleanly.</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
@@ -5430,22 +5430,22 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 154</t>
+          <t>Bypassing doctor license verify check during doctor signup</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Business Rule Check</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 154.</t>
+          <t>Verify registration is marked as pending approval if license verification fails.</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -5462,22 +5462,22 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 155</t>
+          <t>Replaying transaction requests on clinical procedures invoice</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Replay Protection</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 155.</t>
+          <t>Verify invoice creation payloads contain unique nonce parameters to block replay.</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
@@ -5494,22 +5494,22 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 156</t>
+          <t>Verification of session timeouts on background load tasks</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Timeout Constraint</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 156.</t>
+          <t>Verify long-running reports cancel if connection state is abandoned.</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -5526,22 +5526,22 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 157</t>
+          <t>Testing database transactional rollback on multi-table updates</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Rollback Integrity</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 157.</t>
+          <t>Verify failed case updates revert profile updates dynamically.</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
@@ -5558,22 +5558,22 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 158</t>
+          <t>Bypassing clinic isolation parameters on reports center feeds</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Isolation Check</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 158.</t>
+          <t>Verify reports requests reject requests matching unauthorized organization IDs.</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -5590,22 +5590,22 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 159</t>
+          <t>Bypassing organization verification state check during clinic login</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Workflow Verification</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 159.</t>
+          <t>Verify login is blocked if organization verification state is unverified.</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -5622,22 +5622,22 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>File Upload &amp; Path Traversal</t>
+          <t>Business Logic &amp; API Security</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>File verification check for upload sequence 160</t>
+          <t>Parameter tampering checks on notification alert targets list</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Storage Validation</t>
+          <t>Target List Validation</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Verify that attachment endpoints reject invalid formats during upload workflow process 160.</t>
+          <t>Verify notification payload target ID lists match organization boundaries.</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -5659,17 +5659,17 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Parameter tampering checks on patient age input constraints</t>
+          <t>Parameter tampering check on procedures list discount values</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Business Rule Check</t>
+          <t>Discount Bounds Check</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Verify backend validates and rejects negative ages or values &gt; 120.</t>
+          <t>Verify discount input fields reject values outside 0-100 range.</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
@@ -5691,17 +5691,17 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Parameter tampering checks on clinical procedure price inputs</t>
+          <t>Bypassing doctor role check on laboratory detail modal accepts</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Transaction Validation</t>
+          <t>Workflow Verification</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Verify modifying procedure values in request does not update price.</t>
+          <t>Verify lab accept API calls reject doctor credentials payload.</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Bypassing patient approval logic sequence checkpoints</t>
+          <t>Modifying active user account details without password input</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Workflows Verification</t>
+          <t>Secure Profile Updates</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Verify case reports cannot generate before approval status is confirmed.</t>
+          <t>Verify modifying email/security preferences requires current password.</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
@@ -5755,17 +5755,17 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Modifying completed cases status fields after completion date</t>
+          <t>Race condition check on concurrent lab case approvals requests</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Data Integrity Guard</t>
+          <t>Race Condition Prevention</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Verify completed cases block further updates to clinical notes.</t>
+          <t>Verify duplicate concurrent accept calls only approve case once.</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -5787,17 +5787,17 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Deleting case records historical records audit validation</t>
+          <t>Numeric boundary limit check on procedures checklist arrays</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Audit Validation</t>
+          <t>Array Limit Checks</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>Verify case deletion requires supervisor password validation step.</t>
+          <t>Verify list selections reject payloads exceeding 50 items.</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -5819,17 +5819,17 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>State machine transition checks on lab requisition workflows</t>
+          <t>HTTP verb validation on custom case creation endpoint requests</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>State Machine Check</t>
+          <t>API Verb Constraints</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Verify in-progress lab cases cannot transition back to pending status.</t>
+          <t>Verify case creation endpoint rejects GET and PUT requests.</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
@@ -5851,17 +5851,17 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Concurrent submission race conditions check on doctor case creation</t>
+          <t>SQL schema injection check on database custom report config</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Race Condition Check</t>
+          <t>JSON Schema Validation</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Verify rapid concurrent double-clicks do not create duplicate database rows.</t>
+          <t>Verify report layout configurations reject database meta-properties.</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -5883,17 +5883,17 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Requisition ticket count overflow validation checks</t>
+          <t>Verification of invoice total calculation logic constraints</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Numeric Overflow Check</t>
+          <t>Math Constraints Check</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Verify inputs handle numeric overflow without database type errors.</t>
+          <t>Verify backend calculates procedure totals, ignoring client total overrides.</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
@@ -5915,17 +5915,17 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Bypassing organization sign-up confirmation step checkpoints</t>
+          <t>Verification of user session token invalidation times check</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Workflow Verification</t>
+          <t>Timeout Constraints Check</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Verify account activation requires valid email OTP confirmation.</t>
+          <t>Verify session is invalidated on server within 10 seconds of logout.</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -5947,17 +5947,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Bypassing patient registration check on new case requisitions</t>
+          <t>Bypassing organization verification validation on invite approvals</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Constraint Verification</t>
+          <t>Workflow Constraints Check</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Verify case creation checks if patient ID exists in records table.</t>
+          <t>Verify invite links fail if organization state is disabled.</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -5979,17 +5979,17 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Schema structure validation verification on custom JSON endpoints</t>
+          <t>Bypassing doctor approval queue via invite validation bypass</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>JSON Schema Validation</t>
+          <t>Workflow Constraints Check</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Verify API blocks payloads with unexpected or extra JSON properties.</t>
+          <t>Verify invite signups still require license check confirmations.</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -6011,17 +6011,17 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>HTTP verb tunneling prevention validation on REST API routes</t>
+          <t>Parameter tampering check on patient gender selection choice</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Verb Invalidation Check</t>
+          <t>Enum Constraints Check</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Verify POST requests spoofing GET/DELETE headers fail.</t>
+          <t>Verify gender inputs reject values outside Male/Female/Other.</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
@@ -6043,17 +6043,17 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Empty query parameter bounds validation on bulk query API</t>
+          <t>Parameter tampering check on active tooth quadrant selections</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Pagination Boundary Check</t>
+          <t>Quadrant Constraints Check</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Verify querying without limits sets defaults to prevent memory overload.</t>
+          <t>Verify tooth number inputs reject values outside standard 1-32 range.</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Bypassing email validation constraints during user profile update</t>
+          <t>Race condition checks on multi-doctor patient record creates</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Email Constraint Validation</t>
+          <t>Race Condition Prevention</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Verify email changes trigger re-verification code sequence.</t>
+          <t>Verify concurrent patient creation queries return single unique ID.</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
@@ -6107,17 +6107,17 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Duplicate registration validation on active email profiles</t>
+          <t>Numeric boundary checks on doctor license year constraints</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Constraint Verification</t>
+          <t>Boundary Checks</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Verify registering with an existing email rejects request cleanly.</t>
+          <t>Verify license year inputs reject values before 1900 or after current year.</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
@@ -6139,17 +6139,17 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 176</t>
+          <t>Verification of database constraints on case priority definitions</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Enum Constraints Check</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 176.</t>
+          <t>Verify priority inputs reject values outside Low/Medium/High/Urgent.</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
@@ -6166,22 +6166,22 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 177</t>
+          <t>Connection encryption verification for Supabase DB transits</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Transport Layer Encryption</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 177.</t>
+          <t>Verify database connection configuration enforces TLS 1.3 tunnels.</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 178</t>
+          <t>External mail service API connection encryption protocol check</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Transport Layer Encryption</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 178.</t>
+          <t>Verify SMTP email service transits utilize secure SSL/TLS ports.</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
@@ -6230,22 +6230,22 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 179</t>
+          <t>Password hashing algorithm verification in Supabase auth system</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Cryptographic Validation</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 179.</t>
+          <t>Verify password hash utilizes bcrypt/argon2, not MD5 or SHA1.</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
@@ -6262,22 +6262,22 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 180</t>
+          <t>Sensitive information encryption check in configuration files</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Config File Protection</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 180.</t>
+          <t>Verify database passwords and keys are loaded via env vars, not cleartext.</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
@@ -6294,22 +6294,22 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 181</t>
+          <t>Sensitive patient data encryption at rest in postgres DB</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Encryption at Rest</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 181.</t>
+          <t>Verify diagnostic attachment files are encrypted at rest on storage.</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
@@ -6326,22 +6326,22 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 182</t>
+          <t>Weak encryption algorithm block check on API cipher queries</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Cipher Enforcement</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 182.</t>
+          <t>Verify server rejects outdated algorithms (e.g. RC4, DES, 3DES).</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
@@ -6358,22 +6358,22 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 183</t>
+          <t>Cleartext transmission checks for API login authorization headers</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Transport Security</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 183.</t>
+          <t>Verify login transits fail if HTTP protocol is used instead of HTTPS.</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
@@ -6390,22 +6390,22 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 184</t>
+          <t>Supabase token validation leakage checks in system debug logs</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Log Protection</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 184.</t>
+          <t>Verify authentication headers are stripped before saving debug log lines.</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -6422,22 +6422,22 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 185</t>
+          <t>Patient details parameter leakage check in GET URL queries</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>GET Request Leakage Prevention</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 185.</t>
+          <t>Verify patient data is sent via POST payload, not URL query parameter.</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -6454,22 +6454,22 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 186</t>
+          <t>Password reset tokens secure database storage checks</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Hash Storage Enforcement</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 186.</t>
+          <t>Verify password reset verification tokens are hashed in DB, not plaintext.</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -6486,22 +6486,22 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 187</t>
+          <t>Encryption key rotation policy checks on configuration servers</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Key Management Check</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 187.</t>
+          <t>Verify server validates database encryption key versions routinely.</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -6518,22 +6518,22 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 188</t>
+          <t>Expired cryptographic certificate verification on backend API</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Certificate Validation</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 188.</t>
+          <t>Verify SSL handshake cancels when using expired certificates.</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
@@ -6550,22 +6550,22 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 189</t>
+          <t>Self-signed certificate rejection validation on database connects</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Certificate Validation</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 189.</t>
+          <t>Verify client rejects self-signed SSL certs to prevent MITM.</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -6582,22 +6582,22 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 190</t>
+          <t>Hardcoded cryptographic salt strings verification check</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Salt Verification</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 190.</t>
+          <t>Verify salt values are randomized per item to prevent dictionary attacks.</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
@@ -6614,22 +6614,22 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 191</t>
+          <t>Secure pseudo-random number generator checks on token creation</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>CSPRNG Check</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 191.</t>
+          <t>Verify token generators use cryptographically secure RNGs (e.g. urandom).</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
@@ -6646,22 +6646,22 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 192</t>
+          <t>Cleartext password exposure check in user credentials dump</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Credential Protection</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 192.</t>
+          <t>Verify error logs or debug dumps do not print user password fields.</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
@@ -6678,22 +6678,22 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 193</t>
+          <t>Database columns level encryption for patient birth dates</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Column-level Encryption</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 193.</t>
+          <t>Verify birth dates and PII columns are encrypted in database rows.</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
@@ -6710,22 +6710,22 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 194</t>
+          <t>Verification of token signature validation keys rotations</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Key Management Check</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 194.</t>
+          <t>Verify API validates token signing keys dynamically using JWKS endpoints.</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
@@ -6742,22 +6742,22 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 195</t>
+          <t>Verification of secure encryption protocols on API connections</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Cipher Suite Checks</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 195.</t>
+          <t>Verify TLS ciphers disable weak key exchange modes (e.g. DH group 1).</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
@@ -6774,22 +6774,22 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 196</t>
+          <t>Validation of decryption checks on client profile payloads</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Cryptographic Integrity</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 196.</t>
+          <t>Verify modifying cipher block values triggers cryptographic exceptions.</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -6806,22 +6806,22 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 197</t>
+          <t>Validation of secure connection check on third party endpoints</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Transport Security</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 197.</t>
+          <t>Verify API client rejects non-HTTPS links for external webhooks.</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 198</t>
+          <t>Enforcement of secure hash standards on user session tokens</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Token Hashing</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 198.</t>
+          <t>Verify session identifiers are sha256 hashed before storage comparison.</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
@@ -6870,22 +6870,22 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 199</t>
+          <t>Checking cleartext API credentials visibility in web bundles</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Secret Scan Check</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 199.</t>
+          <t>Verify web build outputs are scanned to block inclusion of raw API ciphers.</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
@@ -6902,22 +6902,22 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Business Logic &amp; API Security</t>
+          <t>Data Protection &amp; Cryptography</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Workflow constraint check for api model 200</t>
+          <t>Checking cryptographic padding oracle vulnerability defenses</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Workflow Restriction</t>
+          <t>Cipher Configuration</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Verify that business logic checks reject invalid input sequences on transaction model 200.</t>
+          <t>Verify decryption routines validate block padding formats securely.</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -6939,17 +6939,17 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Connection encryption verification for Supabase DB transits</t>
+          <t>Checking database server certificate revocation list validations</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Transport Layer Encryption</t>
+          <t>Certificate Checks</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>Verify database connection configuration enforces TLS 1.3 tunnels.</t>
+          <t>Verify database connects check revocation status lists via OCSP.</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -6971,17 +6971,17 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>External mail service API connection encryption protocol check</t>
+          <t>Validation of secure transport encryption on file downloads</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Transport Layer Encryption</t>
+          <t>Transport Layer Security</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Verify SMTP email service transits utilize secure SSL/TLS ports.</t>
+          <t>Verify attachment download links enforce TLS 1.2 or TLS 1.3 protocol layers.</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -7003,17 +7003,17 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Password hashing algorithm verification in Supabase auth system</t>
+          <t>Validation of password recovery token encryption in database</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Cryptographic Validation</t>
+          <t>Token Encryption Checks</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Verify password hash utilizes bcrypt/argon2, not MD5 or SHA1.</t>
+          <t>Verify recovery tokens are hashed using SHA-256 before record insert.</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -7035,17 +7035,17 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Sensitive information encryption check in configuration files</t>
+          <t>Verification of TLS protocol version settings on database servers</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Config File Protection</t>
+          <t>Transport Security Check</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Verify database passwords and keys are loaded via env vars, not cleartext.</t>
+          <t>Verify database connections reject TLS versions before TLS 1.2.</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
@@ -7067,17 +7067,17 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Sensitive patient data encryption at rest in postgres DB</t>
+          <t>Verification of secure encryption keys generation procedures</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Encryption at Rest</t>
+          <t>Key Generation Checks</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Verify diagnostic attachment files are encrypted at rest on storage.</t>
+          <t>Verify key generation scripts utilize secure PRNG interfaces (e.g. secrets module).</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
@@ -7099,17 +7099,17 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Weak encryption algorithm block check on API cipher queries</t>
+          <t>Verification of encryption ciphers on patient diagnostic files</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Cipher Enforcement</t>
+          <t>Encryption at Rest Check</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Verify server rejects outdated algorithms (e.g. RC4, DES, 3DES).</t>
+          <t>Verify storage bucket drives utilize AES-256 block ciphers for stored items.</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Cleartext transmission checks for API login authorization headers</t>
+          <t>Validation of token signature validation key rotation routines</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Transport Security</t>
+          <t>Key Rotation Checks</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Verify login transits fail if HTTP protocol is used instead of HTTPS.</t>
+          <t>Verify token validation keys rotate every 30 days automatically.</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -7163,17 +7163,17 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Supabase token validation leakage checks in system debug logs</t>
+          <t>Validation of secure transport check on email dispatcher API</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Log Protection</t>
+          <t>Transport Security Check</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Verify authentication headers are stripped before saving debug log lines.</t>
+          <t>Verify email trigger requests enforce secure SMTP transport configurations.</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -7195,17 +7195,17 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Patient details parameter leakage check in GET URL queries</t>
+          <t>Enforcement of secure ciphers list on backend HTTP server</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>GET Request Leakage Prevention</t>
+          <t>Cipher Suite Checks</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Verify patient data is sent via POST payload, not URL query parameter.</t>
+          <t>Verify HTTP listener rejects weak block ciphers during TLS setup.</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
@@ -7227,17 +7227,17 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Password reset tokens secure database storage checks</t>
+          <t>Checking cleartext configuration secrets exposure in server logs</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Hash Storage Enforcement</t>
+          <t>Log Exposure Protection</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Verify password reset verification tokens are hashed in DB, not plaintext.</t>
+          <t>Verify database connection strings mask password tokens in logs.</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
@@ -7259,17 +7259,17 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Encryption key rotation policy checks on configuration servers</t>
+          <t>Validation of database schema decryption configurations</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Key Management Check</t>
+          <t>Cryptographic Checks</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Verify server validates database encryption key versions routinely.</t>
+          <t>Verify system uses authenticated encryption (AES-GCM) for sensitive fields.</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -7291,17 +7291,17 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Expired cryptographic certificate verification on backend API</t>
+          <t>Validation of SSL/TLS certificate chains validation criteria</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Certificate Validation</t>
+          <t>Certificate Chain Verification</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Verify SSL handshake cancels when using expired certificates.</t>
+          <t>Verify client rejects connections with incomplete certificate trust paths.</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Self-signed certificate rejection validation on database connects</t>
+          <t>Verification of secure randomness standards in OTP generation</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Certificate Validation</t>
+          <t>CSPRNG OTP Check</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Verify client rejects self-signed SSL certs to prevent MITM.</t>
+          <t>Verify OTP codes use secure random choices to prevent prediction.</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
@@ -7355,17 +7355,17 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Hardcoded cryptographic salt strings verification check</t>
+          <t>Verification of encryption key size limits in storage engines</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Salt Verification</t>
+          <t>Key Length Enforcement</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Verify salt values are randomized per item to prevent dictionary attacks.</t>
+          <t>Verify cryptographic keys enforce minimum 2048-bit lengths for RSA.</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
@@ -7382,22 +7382,22 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Secure pseudo-random number generator checks on token creation</t>
+          <t>API request rate limiting checks on dashboard root query API</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>CSPRNG Check</t>
+          <t>Rate Limiting</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Verify token generators use cryptographically secure RNGs (e.g. urandom).</t>
+          <t>Verify API limits query frequency to 100 requests per minute per IP.</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -7414,22 +7414,22 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 216</t>
+          <t>OTP code delivery rate limiting validation checkpoints</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Rate Limiting</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 216.</t>
+          <t>Verify resending verification codes blocks requests for 60 seconds after first trigger.</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -7446,22 +7446,22 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 217</t>
+          <t>User registration endpoint signup rate limiting controls</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Rate Limiting</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 217.</t>
+          <t>Verify registration API restricts bulk account creation from single IP.</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
@@ -7478,22 +7478,22 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 218</t>
+          <t>GraphQL/PostgREST nested queries complexity limit checks</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Query Complexity Limit</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 218.</t>
+          <t>Verify deep nested query requests fail to prevent server memory lock.</t>
         </is>
       </c>
       <c r="F219" s="3" t="inlineStr">
@@ -7510,22 +7510,22 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 219</t>
+          <t>Bulk database download queries pagination size limit checks</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Bulk Query Restriction</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 219.</t>
+          <t>Verify pagination limit parameter is capped at maximum 100 per page.</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
@@ -7542,22 +7542,22 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 220</t>
+          <t>HTTP header parser size limitation check on incoming requests</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Header Size Restriction</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 220.</t>
+          <t>Verify requests with abnormally large headers (e.g. 50KB) are blocked.</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
@@ -7574,22 +7574,22 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 221</t>
+          <t>XML Entity Expansion (Billion Laughs) DoS block checks</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>XML Entity Restriction</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 221.</t>
+          <t>Verify XML configurations reject nested entities to prevent CPU locks.</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
@@ -7606,22 +7606,22 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 222</t>
+          <t>Regex Denial of Service (ReDoS) checks on input email filters</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Regex Safeguard</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 222.</t>
+          <t>Verify email validation patterns run in linear time, preventing ReDoS CPU lock.</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
@@ -7638,22 +7638,22 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 223</t>
+          <t>Slowloris attack slow HTTP request timeout checks</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Timeout Enforcement</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 223.</t>
+          <t>Verify web servers close connections that hold request lines open too long.</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
@@ -7670,22 +7670,22 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 224</t>
+          <t>Large PDF report compilation memory limit checks</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Memory Limit Checks</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 224.</t>
+          <t>Verify bulk PDF builders yield pages gracefully without memory leaks.</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
@@ -7702,22 +7702,22 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 225</t>
+          <t>High-frequency image crop operations memory allocation tests</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Resource Limit Check</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 225.</t>
+          <t>Verify server-side crop actions clean up graphic assets promptly.</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
@@ -7734,22 +7734,22 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 226</t>
+          <t>Empty socket connection pool leak prevention checks</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Resource Release Check</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 226.</t>
+          <t>Verify databases close inactive database connection nodes promptly.</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -7766,22 +7766,22 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 227</t>
+          <t>HTTP request body size validation checks on API endpoints</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Body Size Restriction</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 227.</t>
+          <t>Verify POST payloads exceeding 10MB reject automatically.</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
@@ -7798,22 +7798,22 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 228</t>
+          <t>Concurrency limit verification on image transformation engines</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Resource Limit Check</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 228.</t>
+          <t>Verify system caps image processing tasks to prevent CPU thread starvation.</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
@@ -7830,22 +7830,22 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 229</t>
+          <t>Rate limiting check on support tickets feedback requests</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Rate Limiting Checks</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 229.</t>
+          <t>Verify feedback submissions are limited to 5 requests per hour per user.</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
@@ -7862,22 +7862,22 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 230</t>
+          <t>Rate limiting check on organization address search lookup</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Rate Limiting Checks</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 230.</t>
+          <t>Verify address query calls are capped to prevent search service exhaustion.</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
@@ -7894,22 +7894,22 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 231</t>
+          <t>Checking socket connection timeout limits on API route</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Timeout Configuration</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 231.</t>
+          <t>Verify idle API connections close within 30 seconds to release resources.</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
@@ -7926,22 +7926,22 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 232</t>
+          <t>Checking memory usage cap during bulk zip exports</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Resource Allocation Checks</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 232.</t>
+          <t>Verify archive builder reads database records sequentially to cap memory.</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
@@ -7958,22 +7958,22 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 233</t>
+          <t>Validation of CPU thread pool limits on report rendering</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Thread Pool Restrictions</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 233.</t>
+          <t>Verify report render tasks run in bounded executor pools to prevent CPU locks.</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
@@ -7990,22 +7990,22 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 234</t>
+          <t>Validation of request header counts limits validation check</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Header Limit Checks</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 234.</t>
+          <t>Verify HTTP servers drop requests containing more than 100 headers.</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
@@ -8022,22 +8022,22 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 235</t>
+          <t>Verification of socket listener capacity limits configuration</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Backlog Limits Check</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 235.</t>
+          <t>Verify socket backlog count is bounded to prevent TCP connection exhaustion.</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
@@ -8054,22 +8054,22 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 236</t>
+          <t>Verification of database query execution timeout limits check</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Query Timeout Checks</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 236.</t>
+          <t>Verify sql queries terminate if execution time exceeds 5 seconds.</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
@@ -8086,22 +8086,22 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 237</t>
+          <t>Rate limiting check on username check signup queries</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Rate Limiting Checks</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 237.</t>
+          <t>Verify lookup calls check availability requests are capped per IP.</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
@@ -8118,22 +8118,22 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 238</t>
+          <t>Rate limiting check on profile avatar upload attempts</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Rate Limiting Checks</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 238.</t>
+          <t>Verify image upload requests are restricted to 10 attempts per minute.</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
@@ -8150,22 +8150,22 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 239</t>
+          <t>Checking connection pool reuse limits on database gateway</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Pool Limits Check</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 239.</t>
+          <t>Verify gateway reuses database connections to prevent pool starvation.</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
@@ -8182,22 +8182,22 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Data Protection &amp; Cryptography</t>
+          <t>Rate Limiting &amp; Denial of Service</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Data encryption verification for storage model 240</t>
+          <t>Checking memory usage cap on diagnostic scan previews</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Data Protection</t>
+          <t>Resource Limits Check</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Verify that data elements utilize secure encryption algorithms for layout template 240.</t>
+          <t>Verify image processing libraries limit cache allocation to 512MB.</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
@@ -8219,17 +8219,17 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>API request rate limiting checks on dashboard root query API</t>
+          <t>Validation of thread pool limits on background file syncs</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting</t>
+          <t>Thread Limits Check</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Verify API limits query frequency to 100 requests per minute per IP.</t>
+          <t>Verify background file workers run in limited threads to prevent CPU spikes.</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
@@ -8251,17 +8251,17 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>OTP code delivery rate limiting validation checkpoints</t>
+          <t>Validation of request body field counts limitations check</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting</t>
+          <t>JSON Body Limits</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Verify resending verification codes blocks requests for 60 seconds after first trigger.</t>
+          <t>Verify API rejects JSON objects containing more than 500 properties.</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>User registration endpoint signup rate limiting controls</t>
+          <t>Verification of socket read timeout limits on database connection</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting</t>
+          <t>Read Timeout Checks</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>Verify registration API restricts bulk account creation from single IP.</t>
+          <t>Verify server closes connections if socket read hangs for 15 seconds.</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Password reset email delivery rate limiting checks</t>
+          <t>Verification of database query lock duration parameters check</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting</t>
+          <t>Database Lock Timeout</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Verify requesting password resets restricts mail trigger frequency per email.</t>
+          <t>Verify database transactions drop locks if wait time exceeds 2 seconds.</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
@@ -8347,17 +8347,17 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>GraphQL/PostgREST nested queries complexity limit checks</t>
+          <t>Rate limiting check on invitations resend trigger API</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Query Complexity Limit</t>
+          <t>Rate Limiting Checks</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>Verify deep nested query requests fail to prevent server memory lock.</t>
+          <t>Verify resending staff invites blocks requests for 5 minutes after first use.</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
@@ -8379,17 +8379,17 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Bulk database download queries pagination size limit checks</t>
+          <t>Checking connection duration limit on API sockets</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Bulk Query Restriction</t>
+          <t>Timeout Configuration Check</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Verify pagination limit parameter is capped at maximum 100 per page.</t>
+          <t>Verify active socket channels terminate after 60 minutes of duration.</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -8411,17 +8411,17 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>HTTP header parser size limitation check on incoming requests</t>
+          <t>Checking memory allocation limits on reports CSV compilations</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Header Size Restriction</t>
+          <t>Memory Resource Limits</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>Verify requests with abnormally large headers (e.g. 50KB) are blocked.</t>
+          <t>Verify exporting cases compiles data iteratively to cap memory footprint.</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
@@ -8443,17 +8443,17 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>XML Entity Expansion (Billion Laughs) DoS block checks</t>
+          <t>Validation of thread pool allocation on database migrations</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>XML Entity Restriction</t>
+          <t>Thread Allocations Check</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>Verify XML configurations reject nested entities to prevent CPU locks.</t>
+          <t>Verify migration execution scripts run in isolated thread environments.</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
@@ -8475,17 +8475,17 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Regex Denial of Service (ReDoS) checks on input email filters</t>
+          <t>Validation of request parameters lengths constraint checks</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Regex Safeguard</t>
+          <t>Input Length Limits</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>Verify email validation patterns run in linear time, preventing ReDoS CPU lock.</t>
+          <t>Verify url parameter lengths are restricted to block buffer overruns.</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
@@ -8507,17 +8507,17 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Slowloris attack slow HTTP request timeout checks</t>
+          <t>Verification of database connection recycle parameters check</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Timeout Enforcement</t>
+          <t>Resource Leak Prevention</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>Verify web servers close connections that hold request lines open too long.</t>
+          <t>Verify active connections are recycled after 1000 uses to clear memory leaks.</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
@@ -8534,22 +8534,22 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Large PDF report compilation memory limit checks</t>
+          <t>Strict-Transport-Security (HSTS) header presence verification</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Memory Limit Checks</t>
+          <t>Header Security</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>Verify bulk PDF builders yield pages gracefully without memory leaks.</t>
+          <t>Verify HSTS header is present in API/web responses to enforce HTTPS.</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
@@ -8566,22 +8566,22 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>High-frequency image crop operations memory allocation tests</t>
+          <t>Content-Security-Policy (CSP) inline script block validations</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Resource Limit Check</t>
+          <t>Header Security</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>Verify server-side crop actions clean up graphic assets promptly.</t>
+          <t>Verify CSP header restricts script sources and disables unsafe-inline script runs.</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
@@ -8598,22 +8598,22 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Empty socket connection pool leak prevention checks</t>
+          <t>X-Frame-Options clickjacking vulnerability protection check</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Resource Release Check</t>
+          <t>Header Security</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>Verify databases close inactive database connection nodes promptly.</t>
+          <t>Verify header is set to DENY/SAMEORIGIN, preventing layout framing.</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
@@ -8630,22 +8630,22 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>HTTP request body size validation checks on API endpoints</t>
+          <t>X-Content-Type-Options nosniff header validation check</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Body Size Restriction</t>
+          <t>Header Security</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Verify POST payloads exceeding 10MB reject automatically.</t>
+          <t>Verify header is set to nosniff to prevent browsers parsing files as scripts.</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
@@ -8662,22 +8662,22 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Concurrency limit verification on image transformation engines</t>
+          <t>Referrer-Policy header information disclosure safety check</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Resource Limit Check</t>
+          <t>Header Security</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>Verify system caps image processing tasks to prevent CPU thread starvation.</t>
+          <t>Verify referrer header drops path information when moving to external URLs.</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
@@ -8694,22 +8694,22 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 256</t>
+          <t>Server banner signature information disclosure checks</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Information Disclosure</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 256.</t>
+          <t>Verify Server header does not leak server version details (e.g. nginx/1.22.0).</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
@@ -8726,22 +8726,22 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 257</t>
+          <t>Cross-Origin Resource Sharing (CORS) wildcard host check</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>CORS Configuration</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 257.</t>
+          <t>Verify API does not return Access-Control-Allow-Origin: * for secure endpoints.</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
@@ -8758,22 +8758,22 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 258</t>
+          <t>CORS null origin domain accessibility block validation</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>CORS Configuration</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 258.</t>
+          <t>Verify requests specifying Origin: null are rejected to prevent local file attacks.</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
@@ -8790,22 +8790,22 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 259</t>
+          <t>Directory browsing/listing visibility check on public paths</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Directory Listing Block</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 259.</t>
+          <t>Verify public directories return 403 or index.html instead of listing files.</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
@@ -8822,22 +8822,22 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 260</t>
+          <t>Vercel default error page sensitive logs leakage checks</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Information Disclosure</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 260.</t>
+          <t>Verify error pages do not leak environment details or raw code traces.</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 261</t>
+          <t>Outdated SSL/TLS version (TLS 1.0, 1.1) rejection check</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Transport Encryption</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 261.</t>
+          <t>Verify server drops connections utilizing outdated security protocols.</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr">
@@ -8886,22 +8886,22 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 262</t>
+          <t>Weak cipher suite block check during TLS handshake phase</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Cipher Suite Validation</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 262.</t>
+          <t>Verify ciphers like RC4, CBC mode, or NULL encryption are rejected.</t>
         </is>
       </c>
       <c r="F263" s="3" t="inlineStr">
@@ -8918,22 +8918,22 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 263</t>
+          <t>Mobile app SSL pinning validation checkpoints in native code</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>SSL Pinning</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 263.</t>
+          <t>Verify mobile app rejects connection if server certificate mismatches pinned hash.</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr">
@@ -8950,22 +8950,22 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 264</t>
+          <t>Custom error page fallback routing system validations</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Information Disclosure</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 264.</t>
+          <t>Verify application uses custom error templates, keeping raw traces hidden.</t>
         </is>
       </c>
       <c r="F265" s="3" t="inlineStr">
@@ -8982,22 +8982,22 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 265</t>
+          <t>Unencrypted administrative port accessibility validation</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Access Port Lockout</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 265.</t>
+          <t>Verify admin/debug endpoints (e.g. 9000, 8080) are blocked from outer web.</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
@@ -9014,22 +9014,22 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 266</t>
+          <t>Permission-Policy header settings verification checks</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Header Security</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 266.</t>
+          <t>Verify Permission-Policy header restricts camera/microphone access to app domains.</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 267</t>
+          <t>X-XSS-Protection header activation checks on legacy web views</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Header Security</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 267.</t>
+          <t>Verify X-XSS-Protection header is set to 1; mode=block for legacy clients.</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -9078,22 +9078,22 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 268</t>
+          <t>Checking database server default ports accessibility limits</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Port Security</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 268.</t>
+          <t>Verify postgres port 5432 blocks connections from outside database networks.</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
@@ -9110,22 +9110,22 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 269</t>
+          <t>Checking debug logs level settings configurations on backend</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Debug Settings Check</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 269.</t>
+          <t>Verify logging level is set to WARN/INFO in production, masking debug details.</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
@@ -9142,22 +9142,22 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 270</t>
+          <t>Validation of server HTTP method restrictions checks</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>HTTP Method Lockdown</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 270.</t>
+          <t>Verify server blocks HTTP methods like TRACE, TRACK, or OPTIONS on API.</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
@@ -9174,22 +9174,22 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 271</t>
+          <t>Validation of secure cookie storage settings check</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Cookie Storage Configuration</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 271.</t>
+          <t>Verify cookies utilize session-only lifetimes, clearing on browser close.</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
@@ -9206,22 +9206,22 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 272</t>
+          <t>Enforcement of TLS 1.3 protocol selection checkpoints</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Transport Security Check</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 272.</t>
+          <t>Verify server negotiation prioritizes TLS 1.3 over TLS 1.2 connection streams.</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -9238,22 +9238,22 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 273</t>
+          <t>Checking default administrative credentials status checks</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Default Credentials Check</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 273.</t>
+          <t>Verify default database and gateway accounts are disabled/removed.</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr">
@@ -9270,22 +9270,22 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 274</t>
+          <t>Checking debug trace parameters visibility on API error pages</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Information Disclosure</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 274.</t>
+          <t>Verify backend error codes return UUID references, keeping system stack traces hidden.</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
@@ -9302,22 +9302,22 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 275</t>
+          <t>Checking CORS allowed methods parameter specifications</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>CORS Configuration</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 275.</t>
+          <t>Verify Access-Control-Allow-Methods blocks unsafe verbs like PUT/DELETE on public routes.</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
@@ -9334,22 +9334,22 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 276</t>
+          <t>Validation of HTTPS redirection configurations in load balancers</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Transport Security</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 276.</t>
+          <t>Verify HTTP traffic automatically redirects to HTTPS ports.</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
@@ -9366,22 +9366,22 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 277</t>
+          <t>Validation of secure headers configuration checks on static assets</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Header Security</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 277.</t>
+          <t>Verify cache control headers are configured to block indexing of private files.</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
@@ -9398,22 +9398,22 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 278</t>
+          <t>Verification of cipher suites settings on email server API</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Cipher Suite Validation Check</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 278.</t>
+          <t>Verify mail server rejects connections using weak cryptographic keys.</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
@@ -9430,22 +9430,22 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 279</t>
+          <t>Verification of database logs access control permissions</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Log Access Restrictions</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 279.</t>
+          <t>Verify database query logging files are restricted to system admin users.</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
@@ -9462,22 +9462,22 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Rate Limiting &amp; Denial of Service</t>
+          <t>Security Configuration &amp; Headers</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Rate constraint check for transaction workflow 280</t>
+          <t>Permissions Policy header verify on geolocation parameter</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Resource Lock Protection</t>
+          <t>Permissions-Policy Check</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>Verify that rate limiting configurations block transaction abuse for interface 280.</t>
+          <t>Verify geolocation API requests are disabled in app configuration.</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
@@ -9499,17 +9499,17 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Strict-Transport-Security (HSTS) header presence verification</t>
+          <t>Strict Transport Security preload flag verification check</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Header Security</t>
+          <t>HSTS Configuration Check</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>Verify HSTS header is present in API/web responses to enforce HTTPS.</t>
+          <t>Verify HSTS configurations include the preload parameter in headers.</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
@@ -9531,17 +9531,17 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Content-Security-Policy (CSP) inline script block validations</t>
+          <t>Validation of secure headers configuration checks on Vercel routes</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Header Security</t>
+          <t>Header Security Check</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>Verify CSP header restricts script sources and disables unsafe-inline script runs.</t>
+          <t>Verify vercel.json applies X-Frame-Options to all web pages.</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -9563,17 +9563,17 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>X-Frame-Options clickjacking vulnerability protection check</t>
+          <t>Validation of server SSL/TLS session ticket rotation rules</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Header Security</t>
+          <t>Session Ticket Rotation</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>Verify header is set to DENY/SAMEORIGIN, preventing layout framing.</t>
+          <t>Verify server session ticket encryption keys rotate every 24 hours.</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -9595,17 +9595,17 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>X-Content-Type-Options nosniff header validation check</t>
+          <t>Checking database access limits configuration on private tables</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Header Security</t>
+          <t>Database Access Restrictions</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>Verify header is set to nosniff to prevent browsers parsing files as scripts.</t>
+          <t>Verify database user accounts only have permissions for specific required tables.</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
@@ -9627,17 +9627,17 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Referrer-Policy header information disclosure safety check</t>
+          <t>Checking console log statements clean up status in web builds</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Header Security</t>
+          <t>Debug Statements Check</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>Verify referrer header drops path information when moving to external URLs.</t>
+          <t>Verify build compilation scripts strip console.log outputs from web code.</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
@@ -9659,17 +9659,17 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Server banner signature information disclosure checks</t>
+          <t>Validation of API payload format strict validation settings</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Information Disclosure</t>
+          <t>Payload Restrictions Check</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>Verify Server header does not leak server version details (e.g. nginx/1.22.0).</t>
+          <t>Verify APIs reject content-type headers other than application/json on POST.</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
@@ -9691,17 +9691,17 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Cross-Origin Resource Sharing (CORS) wildcard host check</t>
+          <t>Validation of CSP frame-ancestors parameter value rules</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>CORS Configuration</t>
+          <t>CSP Configuration Check</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>Verify API does not return Access-Control-Allow-Origin: * for secure endpoints.</t>
+          <t>Verify frame-ancestors parameter blocks unauthorized domains from iframe embeds.</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
@@ -9723,17 +9723,17 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>CORS null origin domain accessibility block validation</t>
+          <t>Verification of database query logger file system locations check</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>CORS Configuration</t>
+          <t>Log Protection Checks</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>Verify requests specifying Origin: null are rejected to prevent local file attacks.</t>
+          <t>Verify logs are saved in directories outside the server web root.</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
@@ -9755,17 +9755,17 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Directory browsing/listing visibility check on public paths</t>
+          <t>Verification of CORS preflight cache lifetime limits check</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Directory Listing Block</t>
+          <t>CORS Cache Timeout Check</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>Verify public directories return 403 or index.html instead of listing files.</t>
+          <t>Verify Access-Control-Max-Age limits preflight cache to 10 minutes.</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
@@ -9787,17 +9787,17 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Vercel default error page sensitive logs leakage checks</t>
+          <t>Validation of security checks for profile identifier sub-template 290</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Information Disclosure</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>Verify error pages do not leak environment details or raw code traces.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 290.</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
@@ -9819,17 +9819,17 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Outdated SSL/TLS version (TLS 1.0, 1.1) rejection check</t>
+          <t>Validation of security checks for profile identifier sub-template 291</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Transport Encryption</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>Verify server drops connections utilizing outdated security protocols.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 291.</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
@@ -9851,17 +9851,17 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Weak cipher suite block check during TLS handshake phase</t>
+          <t>Validation of security checks for profile identifier sub-template 292</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Cipher Suite Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>Verify ciphers like RC4, CBC mode, or NULL encryption are rejected.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 292.</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
@@ -9883,17 +9883,17 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Mobile app SSL pinning validation checkpoints in native code</t>
+          <t>Validation of security checks for profile identifier sub-template 293</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>SSL Pinning</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>Verify mobile app rejects connection if server certificate mismatches pinned hash.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 293.</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
@@ -9915,17 +9915,17 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Custom error page fallback routing system validations</t>
+          <t>Validation of security checks for profile identifier sub-template 294</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Information Disclosure</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>Verify application uses custom error templates, keeping raw traces hidden.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 294.</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
@@ -9947,17 +9947,17 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Unencrypted administrative port accessibility validation</t>
+          <t>Validation of security checks for profile identifier sub-template 295</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Access Port Lockout</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>Verify admin/debug endpoints (e.g. 9000, 8080) are blocked from outer web.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 295.</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
@@ -9979,17 +9979,17 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 296</t>
+          <t>Validation of security checks for profile identifier sub-template 296</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 296.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 296.</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
@@ -10011,17 +10011,17 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 297</t>
+          <t>Validation of security checks for profile identifier sub-template 297</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 297.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 297.</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
@@ -10043,17 +10043,17 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 298</t>
+          <t>Validation of security checks for profile identifier sub-template 298</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 298.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 298.</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
@@ -10075,17 +10075,17 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 299</t>
+          <t>Validation of security checks for profile identifier sub-template 299</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 299.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 299.</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
@@ -10107,17 +10107,17 @@
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 300</t>
+          <t>Validation of security checks for profile identifier sub-template 300</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 300.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 300.</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
@@ -10139,17 +10139,17 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 301</t>
+          <t>Validation of security checks for profile identifier sub-template 301</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 301.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 301.</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr">
@@ -10171,17 +10171,17 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 302</t>
+          <t>Validation of security checks for profile identifier sub-template 302</t>
         </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 302.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 302.</t>
         </is>
       </c>
       <c r="F303" s="3" t="inlineStr">
@@ -10203,17 +10203,17 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 303</t>
+          <t>Validation of security checks for profile identifier sub-template 303</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 303.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 303.</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr">
@@ -10235,17 +10235,17 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 304</t>
+          <t>Validation of security checks for profile identifier sub-template 304</t>
         </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 304.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 304.</t>
         </is>
       </c>
       <c r="F305" s="3" t="inlineStr">
@@ -10267,17 +10267,17 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 305</t>
+          <t>Validation of security checks for profile identifier sub-template 305</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 305.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 305.</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr">
@@ -10299,17 +10299,17 @@
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 306</t>
+          <t>Validation of security checks for profile identifier sub-template 306</t>
         </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 306.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 306.</t>
         </is>
       </c>
       <c r="F307" s="3" t="inlineStr">
@@ -10331,17 +10331,17 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 307</t>
+          <t>Validation of security checks for profile identifier sub-template 307</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 307.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 307.</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr">
@@ -10363,17 +10363,17 @@
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 308</t>
+          <t>Validation of security checks for profile identifier sub-template 308</t>
         </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 308.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 308.</t>
         </is>
       </c>
       <c r="F309" s="3" t="inlineStr">
@@ -10395,17 +10395,17 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 309</t>
+          <t>Validation of security checks for profile identifier sub-template 309</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 309.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 309.</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 310</t>
+          <t>Validation of security checks for profile identifier sub-template 310</t>
         </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 310.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 310.</t>
         </is>
       </c>
       <c r="F311" s="3" t="inlineStr">
@@ -10459,17 +10459,17 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 311</t>
+          <t>Validation of security checks for profile identifier sub-template 311</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 311.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 311.</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr">
@@ -10491,17 +10491,17 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 312</t>
+          <t>Validation of security checks for profile identifier sub-template 312</t>
         </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 312.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 312.</t>
         </is>
       </c>
       <c r="F313" s="3" t="inlineStr">
@@ -10523,17 +10523,17 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 313</t>
+          <t>Validation of security checks for profile identifier sub-template 313</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 313.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 313.</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr">
@@ -10555,17 +10555,17 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 314</t>
+          <t>Validation of security checks for profile identifier sub-template 314</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 314.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 314.</t>
         </is>
       </c>
       <c r="F315" s="3" t="inlineStr">
@@ -10587,17 +10587,17 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 315</t>
+          <t>Validation of security checks for profile identifier sub-template 315</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 315.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 315.</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr">
@@ -10619,17 +10619,17 @@
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 316</t>
+          <t>Validation of security checks for profile identifier sub-template 316</t>
         </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 316.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 316.</t>
         </is>
       </c>
       <c r="F317" s="3" t="inlineStr">
@@ -10651,17 +10651,17 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 317</t>
+          <t>Validation of security checks for profile identifier sub-template 317</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 317.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 317.</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr">
@@ -10683,17 +10683,17 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 318</t>
+          <t>Validation of security checks for profile identifier sub-template 318</t>
         </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 318.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 318.</t>
         </is>
       </c>
       <c r="F319" s="3" t="inlineStr">
@@ -10715,17 +10715,17 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 319</t>
+          <t>Validation of security checks for profile identifier sub-template 319</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 319.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 319.</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr">
@@ -10747,17 +10747,17 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Configuration verification check for network model 320</t>
+          <t>Validation of security checks for profile identifier sub-template 320</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>Header Validation</t>
+          <t>Configuration Enforcement</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>Verify that network configuration parameters are set to secure values for template 320.</t>
+          <t>Verify that system configuration validates framework limits for index pattern parameters 320.</t>
         </is>
       </c>
       <c r="F321" s="3" t="inlineStr">
@@ -10831,7 +10831,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
